--- a/气象/气温颜色/气温颜色.xlsx
+++ b/气象/气温颜色/气温颜色.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\文档\GIT SYNC\default\气象\气温颜色\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52C7E6EC-CD80-468F-8D80-14A9E535BF37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E08210F6-5F8F-4590-B744-632CE2B272A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{F39AAB59-546E-453B-99D4-F4E8F2388CF9}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{F39AAB59-546E-453B-99D4-F4E8F2388CF9}"/>
   </bookViews>
   <sheets>
-    <sheet name="渐变色" sheetId="1" r:id="rId1"/>
-    <sheet name="色阶" sheetId="2" r:id="rId2"/>
-    <sheet name="对照表" sheetId="3" r:id="rId3"/>
-    <sheet name="VBA Only" sheetId="4" r:id="rId4"/>
+    <sheet name="V1_配色规则" sheetId="5" r:id="rId1"/>
+    <sheet name="V1_temp" sheetId="6" r:id="rId2"/>
+    <sheet name="V0_渐变色" sheetId="1" r:id="rId3"/>
+    <sheet name="V0_色阶" sheetId="2" r:id="rId4"/>
+    <sheet name="V0_对照表" sheetId="3" r:id="rId5"/>
+    <sheet name="V0_for VBA" sheetId="4" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="953" uniqueCount="265">
   <si>
     <t>249,92,164</t>
   </si>
@@ -586,13 +588,376 @@
   </si>
   <si>
     <t>12,4,5</t>
+  </si>
+  <si>
+    <t>最不冷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基本色</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 相邻两色必须易于分辨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. 实际应用以基本色为基础伸缩区间</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>配色规则</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 冷色调</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 暖色调</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最不热</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 最冷用白色(#ffffff)，最热用黑色(#00000)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第二冷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#ffffff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>第二热</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最热(黑)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>最冷(白)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#000000</t>
+  </si>
+  <si>
+    <t>#000000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对应气温(根据具体项目随时改变)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0℃(0度永远不变)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#4cc9f0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#4895ef</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#4cbff0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#4bb5f0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#4aaaf0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#49a0f0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#4995f0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#4361ee</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#478bef</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#4681ef</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#4576ef</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#446cef</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#4361ef</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#3f37c9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#4359e7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#4251e0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#4148d8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#4040d1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#4037c9</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#3a0ca3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#3e2fc2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#3d26ba</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#3c1eb3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#3b15ab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#3a0ca4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#7209b7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#460ca7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#510bab</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#5c0baf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#670ab3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#730ab7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#b5179e</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#800cb2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#8d0fad</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#9b12a8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#a815a3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#b6189e</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#f72585</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#c31a99</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#d01d94</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#dd208f</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#ea238a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#f9519e</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#fb7db6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#fca8cf</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#fed4e7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>, "</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"),</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#d8d174</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#b6c454</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#8ea604</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#f5bb00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#d76a03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#bf3100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#6fcbd1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#92cdb2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#b5cf93</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#d0ce6c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#c7cb64</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#bfc85c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#acbd40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#a2b52c</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#98ae18</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#a8ac03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#c2b102</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#dcb601</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#eea701</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#e69302</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#df7f03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#d15c03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#cb4e02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#c54001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -634,21 +999,73 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -657,7 +1074,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -696,6 +1113,27 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1010,6 +1448,2462 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF1D7908-26E5-4767-B1D6-50AD24439872}">
+  <dimension ref="A1:C28"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="9.06640625" style="14"/>
+    <col min="2" max="2" width="9.06640625" style="13"/>
+    <col min="3" max="16384" width="9.06640625" style="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="17"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" s="17"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="17"/>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="B3" s="16"/>
+      <c r="C3" s="17"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="B4" s="16"/>
+      <c r="C4" s="17"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="B5" s="16"/>
+      <c r="C5" s="17"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A6" s="17"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="17"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A7" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="B7" s="16"/>
+      <c r="C7" s="17"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A8" s="17"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="17"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A9" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="B9" s="16"/>
+      <c r="C9" s="17" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A10" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A11" s="17"/>
+      <c r="B11" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="C11" s="18">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A12" s="17"/>
+      <c r="B12" s="16" t="s">
+        <v>199</v>
+      </c>
+      <c r="C12" s="18">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A13" s="17"/>
+      <c r="B13" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="C13" s="18">
+        <v>-15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A14" s="17"/>
+      <c r="B14" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="C14" s="18">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A15" s="17"/>
+      <c r="B15" s="16" t="s">
+        <v>217</v>
+      </c>
+      <c r="C15" s="18">
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A16" s="17"/>
+      <c r="B16" s="16" t="s">
+        <v>223</v>
+      </c>
+      <c r="C16" s="18">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A17" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="C17" s="18">
+        <v>-35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A18" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="C18" s="18">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A19" s="17"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="18"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A20" s="17"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="18"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A21" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="B21" s="16"/>
+      <c r="C21" s="18"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A22" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="C22" s="18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A23" s="17"/>
+      <c r="B23" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="C23" s="18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A24" s="17"/>
+      <c r="B24" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="C24" s="18">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A25" s="17"/>
+      <c r="B25" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="C25" s="18">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A26" s="17"/>
+      <c r="B26" s="16" t="s">
+        <v>245</v>
+      </c>
+      <c r="C26" s="18">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A27" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="C27" s="18">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A28" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>189</v>
+      </c>
+      <c r="C28" s="18">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
+  <protectedRanges>
+    <protectedRange sqref="C11:C28" name="区域1"/>
+  </protectedRanges>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A0BF597-3421-4F5A-BD00-F61827AE5752}">
+  <dimension ref="A3:E131"/>
+  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B3">
+        <v>-74</v>
+      </c>
+      <c r="C3" t="s">
+        <v>239</v>
+      </c>
+      <c r="D3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>238</v>
+      </c>
+      <c r="B4">
+        <v>-73</v>
+      </c>
+      <c r="C4" t="s">
+        <v>239</v>
+      </c>
+      <c r="D4" t="s">
+        <v>184</v>
+      </c>
+      <c r="E4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>238</v>
+      </c>
+      <c r="B5">
+        <v>-72</v>
+      </c>
+      <c r="C5" t="s">
+        <v>239</v>
+      </c>
+      <c r="D5" t="s">
+        <v>184</v>
+      </c>
+      <c r="E5" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>238</v>
+      </c>
+      <c r="B6">
+        <v>-71</v>
+      </c>
+      <c r="C6" t="s">
+        <v>239</v>
+      </c>
+      <c r="D6" t="s">
+        <v>184</v>
+      </c>
+      <c r="E6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>238</v>
+      </c>
+      <c r="B7">
+        <v>-70</v>
+      </c>
+      <c r="C7" t="s">
+        <v>239</v>
+      </c>
+      <c r="D7" t="s">
+        <v>184</v>
+      </c>
+      <c r="E7" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>238</v>
+      </c>
+      <c r="B8">
+        <v>-69</v>
+      </c>
+      <c r="C8" t="s">
+        <v>239</v>
+      </c>
+      <c r="D8" t="s">
+        <v>184</v>
+      </c>
+      <c r="E8" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>238</v>
+      </c>
+      <c r="B9">
+        <v>-68</v>
+      </c>
+      <c r="C9" t="s">
+        <v>239</v>
+      </c>
+      <c r="D9" t="s">
+        <v>184</v>
+      </c>
+      <c r="E9" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A10" t="s">
+        <v>238</v>
+      </c>
+      <c r="B10">
+        <v>-67</v>
+      </c>
+      <c r="C10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D10" t="s">
+        <v>184</v>
+      </c>
+      <c r="E10" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>238</v>
+      </c>
+      <c r="B11">
+        <v>-66</v>
+      </c>
+      <c r="C11" t="s">
+        <v>239</v>
+      </c>
+      <c r="D11" t="s">
+        <v>184</v>
+      </c>
+      <c r="E11" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>238</v>
+      </c>
+      <c r="B12">
+        <v>-65</v>
+      </c>
+      <c r="C12" t="s">
+        <v>239</v>
+      </c>
+      <c r="D12" t="s">
+        <v>184</v>
+      </c>
+      <c r="E12" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>238</v>
+      </c>
+      <c r="B13">
+        <v>-64</v>
+      </c>
+      <c r="C13" t="s">
+        <v>239</v>
+      </c>
+      <c r="D13" t="s">
+        <v>184</v>
+      </c>
+      <c r="E13" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A14" t="s">
+        <v>238</v>
+      </c>
+      <c r="B14">
+        <v>-63</v>
+      </c>
+      <c r="C14" t="s">
+        <v>239</v>
+      </c>
+      <c r="D14" t="s">
+        <v>184</v>
+      </c>
+      <c r="E14" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A15" t="s">
+        <v>238</v>
+      </c>
+      <c r="B15">
+        <v>-62</v>
+      </c>
+      <c r="C15" t="s">
+        <v>239</v>
+      </c>
+      <c r="D15" t="s">
+        <v>184</v>
+      </c>
+      <c r="E15" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>238</v>
+      </c>
+      <c r="B16">
+        <v>-61</v>
+      </c>
+      <c r="C16" t="s">
+        <v>239</v>
+      </c>
+      <c r="D16" t="s">
+        <v>184</v>
+      </c>
+      <c r="E16" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>238</v>
+      </c>
+      <c r="B17">
+        <v>-60</v>
+      </c>
+      <c r="C17" t="s">
+        <v>239</v>
+      </c>
+      <c r="D17" t="s">
+        <v>184</v>
+      </c>
+      <c r="E17" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A18" t="s">
+        <v>238</v>
+      </c>
+      <c r="B18">
+        <v>-59</v>
+      </c>
+      <c r="C18" t="s">
+        <v>239</v>
+      </c>
+      <c r="D18" t="s">
+        <v>184</v>
+      </c>
+      <c r="E18" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>238</v>
+      </c>
+      <c r="B19">
+        <v>-58</v>
+      </c>
+      <c r="C19" t="s">
+        <v>239</v>
+      </c>
+      <c r="D19" t="s">
+        <v>184</v>
+      </c>
+      <c r="E19" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>238</v>
+      </c>
+      <c r="B20">
+        <v>-57</v>
+      </c>
+      <c r="C20" t="s">
+        <v>239</v>
+      </c>
+      <c r="D20" t="s">
+        <v>184</v>
+      </c>
+      <c r="E20" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A21" t="s">
+        <v>238</v>
+      </c>
+      <c r="B21">
+        <v>-56</v>
+      </c>
+      <c r="C21" t="s">
+        <v>239</v>
+      </c>
+      <c r="D21" t="s">
+        <v>184</v>
+      </c>
+      <c r="E21" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A22" t="s">
+        <v>238</v>
+      </c>
+      <c r="B22">
+        <v>-55</v>
+      </c>
+      <c r="C22" t="s">
+        <v>239</v>
+      </c>
+      <c r="D22" t="s">
+        <v>184</v>
+      </c>
+      <c r="E22" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A23" t="s">
+        <v>238</v>
+      </c>
+      <c r="B23">
+        <v>-54</v>
+      </c>
+      <c r="C23" t="s">
+        <v>239</v>
+      </c>
+      <c r="D23" t="s">
+        <v>184</v>
+      </c>
+      <c r="E23" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>238</v>
+      </c>
+      <c r="B24">
+        <v>-53</v>
+      </c>
+      <c r="C24" t="s">
+        <v>239</v>
+      </c>
+      <c r="D24" t="s">
+        <v>184</v>
+      </c>
+      <c r="E24" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>238</v>
+      </c>
+      <c r="B25">
+        <v>-52</v>
+      </c>
+      <c r="C25" t="s">
+        <v>239</v>
+      </c>
+      <c r="D25" t="s">
+        <v>184</v>
+      </c>
+      <c r="E25" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A26" t="s">
+        <v>238</v>
+      </c>
+      <c r="B26">
+        <v>-51</v>
+      </c>
+      <c r="C26" t="s">
+        <v>239</v>
+      </c>
+      <c r="D26" t="s">
+        <v>184</v>
+      </c>
+      <c r="E26" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A27" t="s">
+        <v>238</v>
+      </c>
+      <c r="B27">
+        <v>-50</v>
+      </c>
+      <c r="C27" t="s">
+        <v>239</v>
+      </c>
+      <c r="D27" t="s">
+        <v>184</v>
+      </c>
+      <c r="E27" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>238</v>
+      </c>
+      <c r="B28">
+        <v>-49</v>
+      </c>
+      <c r="C28" t="s">
+        <v>239</v>
+      </c>
+      <c r="D28" t="s">
+        <v>184</v>
+      </c>
+      <c r="E28" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>238</v>
+      </c>
+      <c r="B29">
+        <v>-48</v>
+      </c>
+      <c r="C29" t="s">
+        <v>239</v>
+      </c>
+      <c r="D29" t="s">
+        <v>184</v>
+      </c>
+      <c r="E29" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
+        <v>238</v>
+      </c>
+      <c r="B30">
+        <v>-47</v>
+      </c>
+      <c r="C30" t="s">
+        <v>239</v>
+      </c>
+      <c r="D30" t="s">
+        <v>184</v>
+      </c>
+      <c r="E30" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A31" t="s">
+        <v>238</v>
+      </c>
+      <c r="B31">
+        <v>-46</v>
+      </c>
+      <c r="C31" t="s">
+        <v>239</v>
+      </c>
+      <c r="D31" t="s">
+        <v>184</v>
+      </c>
+      <c r="E31" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A32" t="s">
+        <v>238</v>
+      </c>
+      <c r="B32">
+        <v>-45</v>
+      </c>
+      <c r="C32" t="s">
+        <v>239</v>
+      </c>
+      <c r="D32" t="s">
+        <v>184</v>
+      </c>
+      <c r="E32" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A33" t="s">
+        <v>238</v>
+      </c>
+      <c r="B33">
+        <v>-44</v>
+      </c>
+      <c r="C33" t="s">
+        <v>239</v>
+      </c>
+      <c r="D33" t="s">
+        <v>184</v>
+      </c>
+      <c r="E33" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A34" t="s">
+        <v>238</v>
+      </c>
+      <c r="B34">
+        <v>-43</v>
+      </c>
+      <c r="C34" t="s">
+        <v>239</v>
+      </c>
+      <c r="D34" t="s">
+        <v>184</v>
+      </c>
+      <c r="E34" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A35" t="s">
+        <v>238</v>
+      </c>
+      <c r="B35">
+        <v>-42</v>
+      </c>
+      <c r="C35" t="s">
+        <v>239</v>
+      </c>
+      <c r="D35" t="s">
+        <v>184</v>
+      </c>
+      <c r="E35" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A36" t="s">
+        <v>238</v>
+      </c>
+      <c r="B36">
+        <v>-41</v>
+      </c>
+      <c r="C36" t="s">
+        <v>239</v>
+      </c>
+      <c r="D36" t="s">
+        <v>184</v>
+      </c>
+      <c r="E36" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A37" t="s">
+        <v>238</v>
+      </c>
+      <c r="B37">
+        <v>-40</v>
+      </c>
+      <c r="C37" t="s">
+        <v>239</v>
+      </c>
+      <c r="D37" t="s">
+        <v>184</v>
+      </c>
+      <c r="E37" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A38" t="s">
+        <v>238</v>
+      </c>
+      <c r="B38">
+        <v>-39</v>
+      </c>
+      <c r="C38" t="s">
+        <v>239</v>
+      </c>
+      <c r="D38" t="s">
+        <v>237</v>
+      </c>
+      <c r="E38" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A39" t="s">
+        <v>238</v>
+      </c>
+      <c r="B39">
+        <v>-38</v>
+      </c>
+      <c r="C39" t="s">
+        <v>239</v>
+      </c>
+      <c r="D39" t="s">
+        <v>236</v>
+      </c>
+      <c r="E39" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A40" t="s">
+        <v>238</v>
+      </c>
+      <c r="B40">
+        <v>-37</v>
+      </c>
+      <c r="C40" t="s">
+        <v>239</v>
+      </c>
+      <c r="D40" t="s">
+        <v>235</v>
+      </c>
+      <c r="E40" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A41" t="s">
+        <v>238</v>
+      </c>
+      <c r="B41">
+        <v>-36</v>
+      </c>
+      <c r="C41" t="s">
+        <v>239</v>
+      </c>
+      <c r="D41" t="s">
+        <v>234</v>
+      </c>
+      <c r="E41" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A42" t="s">
+        <v>238</v>
+      </c>
+      <c r="B42">
+        <v>-35</v>
+      </c>
+      <c r="C42" t="s">
+        <v>239</v>
+      </c>
+      <c r="D42" t="s">
+        <v>229</v>
+      </c>
+      <c r="E42" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A43" t="s">
+        <v>238</v>
+      </c>
+      <c r="B43">
+        <v>-34</v>
+      </c>
+      <c r="C43" t="s">
+        <v>239</v>
+      </c>
+      <c r="D43" t="s">
+        <v>233</v>
+      </c>
+      <c r="E43" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A44" t="s">
+        <v>238</v>
+      </c>
+      <c r="B44">
+        <v>-33</v>
+      </c>
+      <c r="C44" t="s">
+        <v>239</v>
+      </c>
+      <c r="D44" t="s">
+        <v>232</v>
+      </c>
+      <c r="E44" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A45" t="s">
+        <v>238</v>
+      </c>
+      <c r="B45">
+        <v>-32</v>
+      </c>
+      <c r="C45" t="s">
+        <v>239</v>
+      </c>
+      <c r="D45" t="s">
+        <v>231</v>
+      </c>
+      <c r="E45" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A46" t="s">
+        <v>238</v>
+      </c>
+      <c r="B46">
+        <v>-31</v>
+      </c>
+      <c r="C46" t="s">
+        <v>239</v>
+      </c>
+      <c r="D46" t="s">
+        <v>230</v>
+      </c>
+      <c r="E46" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A47" t="s">
+        <v>238</v>
+      </c>
+      <c r="B47">
+        <v>-30</v>
+      </c>
+      <c r="C47" t="s">
+        <v>239</v>
+      </c>
+      <c r="D47" t="s">
+        <v>228</v>
+      </c>
+      <c r="E47" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A48" t="s">
+        <v>238</v>
+      </c>
+      <c r="B48">
+        <v>-29</v>
+      </c>
+      <c r="C48" t="s">
+        <v>239</v>
+      </c>
+      <c r="D48" t="s">
+        <v>227</v>
+      </c>
+      <c r="E48" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A49" t="s">
+        <v>238</v>
+      </c>
+      <c r="B49">
+        <v>-28</v>
+      </c>
+      <c r="C49" t="s">
+        <v>239</v>
+      </c>
+      <c r="D49" t="s">
+        <v>226</v>
+      </c>
+      <c r="E49" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A50" t="s">
+        <v>238</v>
+      </c>
+      <c r="B50">
+        <v>-27</v>
+      </c>
+      <c r="C50" t="s">
+        <v>239</v>
+      </c>
+      <c r="D50" t="s">
+        <v>225</v>
+      </c>
+      <c r="E50" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A51" t="s">
+        <v>238</v>
+      </c>
+      <c r="B51">
+        <v>-26</v>
+      </c>
+      <c r="C51" t="s">
+        <v>239</v>
+      </c>
+      <c r="D51" t="s">
+        <v>224</v>
+      </c>
+      <c r="E51" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A52" t="s">
+        <v>238</v>
+      </c>
+      <c r="B52">
+        <v>-25</v>
+      </c>
+      <c r="C52" t="s">
+        <v>239</v>
+      </c>
+      <c r="D52" t="s">
+        <v>222</v>
+      </c>
+      <c r="E52" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A53" t="s">
+        <v>238</v>
+      </c>
+      <c r="B53">
+        <v>-24</v>
+      </c>
+      <c r="C53" t="s">
+        <v>239</v>
+      </c>
+      <c r="D53" t="s">
+        <v>221</v>
+      </c>
+      <c r="E53" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A54" t="s">
+        <v>238</v>
+      </c>
+      <c r="B54">
+        <v>-23</v>
+      </c>
+      <c r="C54" t="s">
+        <v>239</v>
+      </c>
+      <c r="D54" t="s">
+        <v>220</v>
+      </c>
+      <c r="E54" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A55" t="s">
+        <v>238</v>
+      </c>
+      <c r="B55">
+        <v>-22</v>
+      </c>
+      <c r="C55" t="s">
+        <v>239</v>
+      </c>
+      <c r="D55" t="s">
+        <v>219</v>
+      </c>
+      <c r="E55" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A56" t="s">
+        <v>238</v>
+      </c>
+      <c r="B56">
+        <v>-21</v>
+      </c>
+      <c r="C56" t="s">
+        <v>239</v>
+      </c>
+      <c r="D56" t="s">
+        <v>218</v>
+      </c>
+      <c r="E56" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A57" t="s">
+        <v>238</v>
+      </c>
+      <c r="B57">
+        <v>-20</v>
+      </c>
+      <c r="C57" t="s">
+        <v>239</v>
+      </c>
+      <c r="D57" t="s">
+        <v>216</v>
+      </c>
+      <c r="E57" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A58" t="s">
+        <v>238</v>
+      </c>
+      <c r="B58">
+        <v>-19</v>
+      </c>
+      <c r="C58" t="s">
+        <v>239</v>
+      </c>
+      <c r="D58" t="s">
+        <v>215</v>
+      </c>
+      <c r="E58" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A59" t="s">
+        <v>238</v>
+      </c>
+      <c r="B59">
+        <v>-18</v>
+      </c>
+      <c r="C59" t="s">
+        <v>239</v>
+      </c>
+      <c r="D59" t="s">
+        <v>214</v>
+      </c>
+      <c r="E59" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A60" t="s">
+        <v>238</v>
+      </c>
+      <c r="B60">
+        <v>-17</v>
+      </c>
+      <c r="C60" t="s">
+        <v>239</v>
+      </c>
+      <c r="D60" t="s">
+        <v>213</v>
+      </c>
+      <c r="E60" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A61" t="s">
+        <v>238</v>
+      </c>
+      <c r="B61">
+        <v>-16</v>
+      </c>
+      <c r="C61" t="s">
+        <v>239</v>
+      </c>
+      <c r="D61" t="s">
+        <v>212</v>
+      </c>
+      <c r="E61" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A62" t="s">
+        <v>238</v>
+      </c>
+      <c r="B62">
+        <v>-15</v>
+      </c>
+      <c r="C62" t="s">
+        <v>239</v>
+      </c>
+      <c r="D62" t="s">
+        <v>210</v>
+      </c>
+      <c r="E62" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A63" t="s">
+        <v>238</v>
+      </c>
+      <c r="B63">
+        <v>-14</v>
+      </c>
+      <c r="C63" t="s">
+        <v>239</v>
+      </c>
+      <c r="D63" t="s">
+        <v>209</v>
+      </c>
+      <c r="E63" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A64" t="s">
+        <v>238</v>
+      </c>
+      <c r="B64">
+        <v>-13</v>
+      </c>
+      <c r="C64" t="s">
+        <v>239</v>
+      </c>
+      <c r="D64" t="s">
+        <v>208</v>
+      </c>
+      <c r="E64" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A65" t="s">
+        <v>238</v>
+      </c>
+      <c r="B65">
+        <v>-12</v>
+      </c>
+      <c r="C65" t="s">
+        <v>239</v>
+      </c>
+      <c r="D65" t="s">
+        <v>207</v>
+      </c>
+      <c r="E65" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A66" t="s">
+        <v>238</v>
+      </c>
+      <c r="B66">
+        <v>-11</v>
+      </c>
+      <c r="C66" t="s">
+        <v>239</v>
+      </c>
+      <c r="D66" t="s">
+        <v>206</v>
+      </c>
+      <c r="E66" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A67" t="s">
+        <v>238</v>
+      </c>
+      <c r="B67">
+        <v>-10</v>
+      </c>
+      <c r="C67" t="s">
+        <v>239</v>
+      </c>
+      <c r="D67" t="s">
+        <v>204</v>
+      </c>
+      <c r="E67" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A68" t="s">
+        <v>238</v>
+      </c>
+      <c r="B68">
+        <v>-9</v>
+      </c>
+      <c r="C68" t="s">
+        <v>239</v>
+      </c>
+      <c r="D68" t="s">
+        <v>203</v>
+      </c>
+      <c r="E68" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A69" t="s">
+        <v>238</v>
+      </c>
+      <c r="B69">
+        <v>-8</v>
+      </c>
+      <c r="C69" t="s">
+        <v>239</v>
+      </c>
+      <c r="D69" t="s">
+        <v>202</v>
+      </c>
+      <c r="E69" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A70" t="s">
+        <v>238</v>
+      </c>
+      <c r="B70">
+        <v>-7</v>
+      </c>
+      <c r="C70" t="s">
+        <v>239</v>
+      </c>
+      <c r="D70" t="s">
+        <v>201</v>
+      </c>
+      <c r="E70" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A71" t="s">
+        <v>238</v>
+      </c>
+      <c r="B71">
+        <v>-6</v>
+      </c>
+      <c r="C71" t="s">
+        <v>239</v>
+      </c>
+      <c r="D71" t="s">
+        <v>200</v>
+      </c>
+      <c r="E71" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A72" t="s">
+        <v>238</v>
+      </c>
+      <c r="B72">
+        <v>-5</v>
+      </c>
+      <c r="C72" t="s">
+        <v>239</v>
+      </c>
+      <c r="D72" t="s">
+        <v>198</v>
+      </c>
+      <c r="E72" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A73" t="s">
+        <v>238</v>
+      </c>
+      <c r="B73">
+        <v>-4</v>
+      </c>
+      <c r="C73" t="s">
+        <v>239</v>
+      </c>
+      <c r="D73" t="s">
+        <v>197</v>
+      </c>
+      <c r="E73" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A74" t="s">
+        <v>238</v>
+      </c>
+      <c r="B74">
+        <v>-3</v>
+      </c>
+      <c r="C74" t="s">
+        <v>239</v>
+      </c>
+      <c r="D74" t="s">
+        <v>196</v>
+      </c>
+      <c r="E74" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A75" t="s">
+        <v>238</v>
+      </c>
+      <c r="B75">
+        <v>-2</v>
+      </c>
+      <c r="C75" t="s">
+        <v>239</v>
+      </c>
+      <c r="D75" t="s">
+        <v>195</v>
+      </c>
+      <c r="E75" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A76" t="s">
+        <v>238</v>
+      </c>
+      <c r="B76">
+        <v>-1</v>
+      </c>
+      <c r="C76" t="s">
+        <v>239</v>
+      </c>
+      <c r="D76" t="s">
+        <v>194</v>
+      </c>
+      <c r="E76" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A77" t="s">
+        <v>238</v>
+      </c>
+      <c r="B77">
+        <v>0</v>
+      </c>
+      <c r="C77" t="s">
+        <v>239</v>
+      </c>
+      <c r="D77" t="s">
+        <v>192</v>
+      </c>
+      <c r="E77" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A78" t="s">
+        <v>238</v>
+      </c>
+      <c r="B78">
+        <v>1</v>
+      </c>
+      <c r="C78" t="s">
+        <v>239</v>
+      </c>
+      <c r="D78" t="s">
+        <v>247</v>
+      </c>
+      <c r="E78" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A79" t="s">
+        <v>238</v>
+      </c>
+      <c r="B79">
+        <v>2</v>
+      </c>
+      <c r="C79" t="s">
+        <v>239</v>
+      </c>
+      <c r="D79" t="s">
+        <v>248</v>
+      </c>
+      <c r="E79" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A80" t="s">
+        <v>238</v>
+      </c>
+      <c r="B80">
+        <v>3</v>
+      </c>
+      <c r="C80" t="s">
+        <v>239</v>
+      </c>
+      <c r="D80" t="s">
+        <v>249</v>
+      </c>
+      <c r="E80" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A81" t="s">
+        <v>238</v>
+      </c>
+      <c r="B81">
+        <v>4</v>
+      </c>
+      <c r="C81" t="s">
+        <v>239</v>
+      </c>
+      <c r="D81" t="s">
+        <v>241</v>
+      </c>
+      <c r="E81" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A82" t="s">
+        <v>238</v>
+      </c>
+      <c r="B82">
+        <v>5</v>
+      </c>
+      <c r="C82" t="s">
+        <v>239</v>
+      </c>
+      <c r="D82" t="s">
+        <v>250</v>
+      </c>
+      <c r="E82" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A83" t="s">
+        <v>238</v>
+      </c>
+      <c r="B83">
+        <v>6</v>
+      </c>
+      <c r="C83" t="s">
+        <v>239</v>
+      </c>
+      <c r="D83" t="s">
+        <v>251</v>
+      </c>
+      <c r="E83" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A84" t="s">
+        <v>238</v>
+      </c>
+      <c r="B84">
+        <v>7</v>
+      </c>
+      <c r="C84" t="s">
+        <v>239</v>
+      </c>
+      <c r="D84" t="s">
+        <v>252</v>
+      </c>
+      <c r="E84" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A85" t="s">
+        <v>238</v>
+      </c>
+      <c r="B85">
+        <v>8</v>
+      </c>
+      <c r="C85" t="s">
+        <v>239</v>
+      </c>
+      <c r="D85" t="s">
+        <v>242</v>
+      </c>
+      <c r="E85" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A86" t="s">
+        <v>238</v>
+      </c>
+      <c r="B86">
+        <v>9</v>
+      </c>
+      <c r="C86" t="s">
+        <v>239</v>
+      </c>
+      <c r="D86" t="s">
+        <v>253</v>
+      </c>
+      <c r="E86" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A87" t="s">
+        <v>238</v>
+      </c>
+      <c r="B87">
+        <v>10</v>
+      </c>
+      <c r="C87" t="s">
+        <v>239</v>
+      </c>
+      <c r="D87" t="s">
+        <v>254</v>
+      </c>
+      <c r="E87" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A88" t="s">
+        <v>238</v>
+      </c>
+      <c r="B88">
+        <v>11</v>
+      </c>
+      <c r="C88" t="s">
+        <v>239</v>
+      </c>
+      <c r="D88" t="s">
+        <v>255</v>
+      </c>
+      <c r="E88" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A89" t="s">
+        <v>238</v>
+      </c>
+      <c r="B89">
+        <v>12</v>
+      </c>
+      <c r="C89" t="s">
+        <v>239</v>
+      </c>
+      <c r="D89" t="s">
+        <v>243</v>
+      </c>
+      <c r="E89" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A90" t="s">
+        <v>238</v>
+      </c>
+      <c r="B90">
+        <v>13</v>
+      </c>
+      <c r="C90" t="s">
+        <v>239</v>
+      </c>
+      <c r="D90" t="s">
+        <v>256</v>
+      </c>
+      <c r="E90" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A91" t="s">
+        <v>238</v>
+      </c>
+      <c r="B91">
+        <v>14</v>
+      </c>
+      <c r="C91" t="s">
+        <v>239</v>
+      </c>
+      <c r="D91" t="s">
+        <v>257</v>
+      </c>
+      <c r="E91" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A92" t="s">
+        <v>238</v>
+      </c>
+      <c r="B92">
+        <v>15</v>
+      </c>
+      <c r="C92" t="s">
+        <v>239</v>
+      </c>
+      <c r="D92" t="s">
+        <v>258</v>
+      </c>
+      <c r="E92" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A93" t="s">
+        <v>238</v>
+      </c>
+      <c r="B93">
+        <v>16</v>
+      </c>
+      <c r="C93" t="s">
+        <v>239</v>
+      </c>
+      <c r="D93" t="s">
+        <v>244</v>
+      </c>
+      <c r="E93" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A94" t="s">
+        <v>238</v>
+      </c>
+      <c r="B94">
+        <v>17</v>
+      </c>
+      <c r="C94" t="s">
+        <v>239</v>
+      </c>
+      <c r="D94" t="s">
+        <v>259</v>
+      </c>
+      <c r="E94" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A95" t="s">
+        <v>238</v>
+      </c>
+      <c r="B95">
+        <v>18</v>
+      </c>
+      <c r="C95" t="s">
+        <v>239</v>
+      </c>
+      <c r="D95" t="s">
+        <v>260</v>
+      </c>
+      <c r="E95" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A96" t="s">
+        <v>238</v>
+      </c>
+      <c r="B96">
+        <v>19</v>
+      </c>
+      <c r="C96" t="s">
+        <v>239</v>
+      </c>
+      <c r="D96" t="s">
+        <v>261</v>
+      </c>
+      <c r="E96" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A97" t="s">
+        <v>238</v>
+      </c>
+      <c r="B97">
+        <v>20</v>
+      </c>
+      <c r="C97" t="s">
+        <v>239</v>
+      </c>
+      <c r="D97" t="s">
+        <v>245</v>
+      </c>
+      <c r="E97" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A98" t="s">
+        <v>238</v>
+      </c>
+      <c r="B98">
+        <v>21</v>
+      </c>
+      <c r="C98" t="s">
+        <v>239</v>
+      </c>
+      <c r="D98" t="s">
+        <v>262</v>
+      </c>
+      <c r="E98" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A99" t="s">
+        <v>238</v>
+      </c>
+      <c r="B99">
+        <v>22</v>
+      </c>
+      <c r="C99" t="s">
+        <v>239</v>
+      </c>
+      <c r="D99" t="s">
+        <v>263</v>
+      </c>
+      <c r="E99" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A100" t="s">
+        <v>238</v>
+      </c>
+      <c r="B100">
+        <v>23</v>
+      </c>
+      <c r="C100" t="s">
+        <v>239</v>
+      </c>
+      <c r="D100" t="s">
+        <v>264</v>
+      </c>
+      <c r="E100" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A101" t="s">
+        <v>238</v>
+      </c>
+      <c r="B101">
+        <v>24</v>
+      </c>
+      <c r="C101" t="s">
+        <v>239</v>
+      </c>
+      <c r="D101" t="s">
+        <v>246</v>
+      </c>
+      <c r="E101" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A102" t="s">
+        <v>238</v>
+      </c>
+      <c r="B102">
+        <v>25</v>
+      </c>
+      <c r="C102" t="s">
+        <v>239</v>
+      </c>
+      <c r="D102" t="s">
+        <v>188</v>
+      </c>
+      <c r="E102" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A103" t="s">
+        <v>238</v>
+      </c>
+      <c r="B103">
+        <v>26</v>
+      </c>
+      <c r="C103" t="s">
+        <v>239</v>
+      </c>
+      <c r="D103" t="s">
+        <v>188</v>
+      </c>
+      <c r="E103" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A104" t="s">
+        <v>238</v>
+      </c>
+      <c r="B104">
+        <v>27</v>
+      </c>
+      <c r="C104" t="s">
+        <v>239</v>
+      </c>
+      <c r="D104" t="s">
+        <v>188</v>
+      </c>
+      <c r="E104" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A105" t="s">
+        <v>238</v>
+      </c>
+      <c r="B105">
+        <v>28</v>
+      </c>
+      <c r="C105" t="s">
+        <v>239</v>
+      </c>
+      <c r="D105" t="s">
+        <v>188</v>
+      </c>
+      <c r="E105" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A106" t="s">
+        <v>238</v>
+      </c>
+      <c r="B106">
+        <v>29</v>
+      </c>
+      <c r="C106" t="s">
+        <v>239</v>
+      </c>
+      <c r="D106" t="s">
+        <v>188</v>
+      </c>
+      <c r="E106" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A107" t="s">
+        <v>238</v>
+      </c>
+      <c r="B107">
+        <v>30</v>
+      </c>
+      <c r="C107" t="s">
+        <v>239</v>
+      </c>
+      <c r="D107" t="s">
+        <v>188</v>
+      </c>
+      <c r="E107" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A108" t="s">
+        <v>238</v>
+      </c>
+      <c r="B108">
+        <v>31</v>
+      </c>
+      <c r="C108" t="s">
+        <v>239</v>
+      </c>
+      <c r="D108" t="s">
+        <v>188</v>
+      </c>
+      <c r="E108" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A109" t="s">
+        <v>238</v>
+      </c>
+      <c r="B109">
+        <v>32</v>
+      </c>
+      <c r="C109" t="s">
+        <v>239</v>
+      </c>
+      <c r="D109" t="s">
+        <v>188</v>
+      </c>
+      <c r="E109" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A110" t="s">
+        <v>238</v>
+      </c>
+      <c r="B110">
+        <v>33</v>
+      </c>
+      <c r="C110" t="s">
+        <v>239</v>
+      </c>
+      <c r="D110" t="s">
+        <v>188</v>
+      </c>
+      <c r="E110" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A111" t="s">
+        <v>238</v>
+      </c>
+      <c r="B111">
+        <v>34</v>
+      </c>
+      <c r="C111" t="s">
+        <v>239</v>
+      </c>
+      <c r="D111" t="s">
+        <v>188</v>
+      </c>
+      <c r="E111" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A112" t="s">
+        <v>238</v>
+      </c>
+      <c r="B112">
+        <v>35</v>
+      </c>
+      <c r="C112" t="s">
+        <v>239</v>
+      </c>
+      <c r="D112" t="s">
+        <v>188</v>
+      </c>
+      <c r="E112" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A113" t="s">
+        <v>238</v>
+      </c>
+      <c r="B113">
+        <v>36</v>
+      </c>
+      <c r="C113" t="s">
+        <v>239</v>
+      </c>
+      <c r="D113" t="s">
+        <v>188</v>
+      </c>
+      <c r="E113" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A114" t="s">
+        <v>238</v>
+      </c>
+      <c r="B114">
+        <v>37</v>
+      </c>
+      <c r="C114" t="s">
+        <v>239</v>
+      </c>
+      <c r="D114" t="s">
+        <v>188</v>
+      </c>
+      <c r="E114" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A115" t="s">
+        <v>238</v>
+      </c>
+      <c r="B115">
+        <v>38</v>
+      </c>
+      <c r="C115" t="s">
+        <v>239</v>
+      </c>
+      <c r="D115" t="s">
+        <v>188</v>
+      </c>
+      <c r="E115" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A116" t="s">
+        <v>238</v>
+      </c>
+      <c r="B116">
+        <v>39</v>
+      </c>
+      <c r="C116" t="s">
+        <v>239</v>
+      </c>
+      <c r="D116" t="s">
+        <v>188</v>
+      </c>
+      <c r="E116" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A117" t="s">
+        <v>238</v>
+      </c>
+      <c r="B117">
+        <v>40</v>
+      </c>
+      <c r="C117" t="s">
+        <v>239</v>
+      </c>
+      <c r="D117" t="s">
+        <v>188</v>
+      </c>
+      <c r="E117" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A118" t="s">
+        <v>238</v>
+      </c>
+      <c r="B118">
+        <v>41</v>
+      </c>
+      <c r="C118" t="s">
+        <v>239</v>
+      </c>
+      <c r="D118" t="s">
+        <v>188</v>
+      </c>
+      <c r="E118" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A119" t="s">
+        <v>238</v>
+      </c>
+      <c r="B119">
+        <v>42</v>
+      </c>
+      <c r="C119" t="s">
+        <v>239</v>
+      </c>
+      <c r="D119" t="s">
+        <v>188</v>
+      </c>
+      <c r="E119" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A120" t="s">
+        <v>238</v>
+      </c>
+      <c r="B120">
+        <v>43</v>
+      </c>
+      <c r="C120" t="s">
+        <v>239</v>
+      </c>
+      <c r="D120" t="s">
+        <v>188</v>
+      </c>
+      <c r="E120" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A121" t="s">
+        <v>238</v>
+      </c>
+      <c r="B121">
+        <v>44</v>
+      </c>
+      <c r="C121" t="s">
+        <v>239</v>
+      </c>
+      <c r="D121" t="s">
+        <v>188</v>
+      </c>
+      <c r="E121" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A122" t="s">
+        <v>238</v>
+      </c>
+      <c r="B122">
+        <v>45</v>
+      </c>
+      <c r="C122" t="s">
+        <v>239</v>
+      </c>
+      <c r="D122" t="s">
+        <v>188</v>
+      </c>
+      <c r="E122" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A123" t="s">
+        <v>238</v>
+      </c>
+      <c r="B123">
+        <v>46</v>
+      </c>
+      <c r="C123" t="s">
+        <v>239</v>
+      </c>
+      <c r="D123" t="s">
+        <v>188</v>
+      </c>
+      <c r="E123" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A124" t="s">
+        <v>238</v>
+      </c>
+      <c r="B124">
+        <v>47</v>
+      </c>
+      <c r="C124" t="s">
+        <v>239</v>
+      </c>
+      <c r="D124" t="s">
+        <v>188</v>
+      </c>
+      <c r="E124" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A125" t="s">
+        <v>238</v>
+      </c>
+      <c r="B125">
+        <v>48</v>
+      </c>
+      <c r="C125" t="s">
+        <v>239</v>
+      </c>
+      <c r="D125" t="s">
+        <v>188</v>
+      </c>
+      <c r="E125" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A126" t="s">
+        <v>238</v>
+      </c>
+      <c r="B126">
+        <v>49</v>
+      </c>
+      <c r="C126" t="s">
+        <v>239</v>
+      </c>
+      <c r="D126" t="s">
+        <v>188</v>
+      </c>
+      <c r="E126" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A127" t="s">
+        <v>238</v>
+      </c>
+      <c r="B127">
+        <v>50</v>
+      </c>
+      <c r="C127" t="s">
+        <v>239</v>
+      </c>
+      <c r="D127" t="s">
+        <v>188</v>
+      </c>
+      <c r="E127" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A128" t="s">
+        <v>238</v>
+      </c>
+      <c r="B128">
+        <v>51</v>
+      </c>
+      <c r="C128" t="s">
+        <v>239</v>
+      </c>
+      <c r="D128" t="s">
+        <v>188</v>
+      </c>
+      <c r="E128" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A129" t="s">
+        <v>238</v>
+      </c>
+      <c r="B129">
+        <v>52</v>
+      </c>
+      <c r="C129" t="s">
+        <v>239</v>
+      </c>
+      <c r="D129" t="s">
+        <v>188</v>
+      </c>
+      <c r="E129" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A130" t="s">
+        <v>238</v>
+      </c>
+      <c r="B130">
+        <v>53</v>
+      </c>
+      <c r="C130" t="s">
+        <v>239</v>
+      </c>
+      <c r="D130" t="s">
+        <v>188</v>
+      </c>
+      <c r="E130" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A131" t="s">
+        <v>238</v>
+      </c>
+      <c r="B131">
+        <v>54</v>
+      </c>
+      <c r="C131" t="s">
+        <v>239</v>
+      </c>
+      <c r="D131" t="s">
+        <v>188</v>
+      </c>
+      <c r="E131" t="s">
+        <v>240</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D51A6BCF-4E21-4F18-8E61-CFE627055BDA}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:E29"/>
@@ -1418,7 +4312,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D665CAA-C18E-4815-A9FE-2BA2EAE7CC94}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:J53"/>
@@ -2488,7 +5382,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB8C5B0E-C5AA-4C2F-B2EF-41D89B3B9623}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:B28"/>
@@ -2727,7 +5621,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80B72386-D55D-4684-95DC-E015852A389A}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A2:B132"/>
